--- a/input/mapping/089. OCB_GOLD_TTDL_TBL_BPM_TCDV_LINK_LINH.xlsx
+++ b/input/mapping/089. OCB_GOLD_TTDL_TBL_BPM_TCDV_LINK_LINH.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30408"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30404"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="9" documentId="6_{17506A6E-C14E-43F5-8A78-3295F85DD674}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{72121BEA-8A91-41D8-97D9-279654C3DB5F}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="6_{17506A6E-C14E-43F5-8A78-3295F85DD674}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{42103D35-67BF-449F-B01A-349B96B42A5B}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="2" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="6" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="50">
   <si>
     <t>TBL_BPM_TCDV_LINK —  Data Lineage Summary</t>
   </si>
@@ -71,10 +71,13 @@
     <t>TBL_BPM_TCDV_LINK</t>
   </si>
   <si>
-    <t>hub_auth_to_chuc_dvi_link</t>
-  </si>
-  <si>
-    <t>sat_auth_to_chuc_dvi_link</t>
+    <t>effsat_link_auth_to_chuc_dvi_link</t>
+  </si>
+  <si>
+    <t>link_auth_to_chuc_dvi_link</t>
+  </si>
+  <si>
+    <t>hub_auth_to_chuc_don_vi</t>
   </si>
   <si>
     <t>LEGEND</t>
@@ -131,30 +134,47 @@
     <t xml:space="preserve">code mới </t>
   </si>
   <si>
-    <t xml:space="preserve">USE CATALOG IDENTIFIER(:curated);
+    <t xml:space="preserve">
+USE CATALOG IDENTIFIER(:curated);
 USE SCHEMA gstx;
-CREATE OR REPLACE TABLE TBL_BPM_TCDV_LINK AS
-WITH 
+INSERT OVERWRITE TBL_BPM_TCDV_LINK
+(
+    id, don_vi_goc_id, don_vi_lket_id
+)
+WITH
+-- ban ghi effectivity moi nhat cua tung link, chi giu link dang active
+dvi_link_eff AS (
+    SELECT link_auth_to_chuc_dvi_link_hashkey,
+           max_by(active_flag, source_event_date) AS active_flag
+    FROM IDENTIFIER(:cleaned || '.raw_vault.effsat_link_auth_to_chuc_dvi_link')
+    WHERE source_event_date &lt;= TO_DATE(:target_date, 'yyyyMMdd')
+    GROUP BY link_auth_to_chuc_dvi_link_hashkey
+),
 dvi_link_active AS (
-    SELECT h.auth_to_chuc_dvi_link_hashkey, h.business_key
-    FROM IDENTIFIER(:cleaned || '.raw_vault.hub_auth_to_chuc_dvi_link') h
-    WHERE h.source_event_date &lt;= TO_DATE(:DATADT, 'yyyyMMdd')
+    SELECT l.link_auth_to_chuc_dvi_link_hashkey,
+           l.don_vi_goc_hashkey,
+           l.don_vi_lket_hashkey
+    FROM IDENTIFIER(:cleaned || '.raw_vault.link_auth_to_chuc_dvi_link') l
+    JOIN dvi_link_eff e
+      ON e.link_auth_to_chuc_dvi_link_hashkey = l.link_auth_to_chuc_dvi_link_hashkey
+    WHERE l.source_event_date &lt;= TO_DATE(:target_date, 'yyyyMMdd')
+      AND e.active_flag = 1
 ),
-dvi_link_sat AS (
-    SELECT auth_to_chuc_dvi_link_hashkey,
-           max_by(don_vi_goc_id,  source_event_date) AS don_vi_goc_id,
-           max_by(don_vi_lket_id, source_event_date) AS don_vi_lket_id
-    FROM IDENTIFIER(:cleaned || '.raw_vault.sat_auth_to_chuc_dvi_link')
-    WHERE source_event_date &lt;= TO_DATE(:DATADT, 'yyyyMMdd')
-    GROUP BY auth_to_chuc_dvi_link_hashkey
+don_vi AS (
+    SELECT auth_to_chuc_don_vi_hashkey,
+           max_by(business_key, source_event_date) AS business_key
+    FROM IDENTIFIER(:cleaned || '.raw_vault.hub_auth_to_chuc_don_vi')
+    WHERE source_event_date &lt;= TO_DATE(:target_date, 'yyyyMMdd')
+    GROUP BY auth_to_chuc_don_vi_hashkey
 )
 SELECT
-      h.business_key     AS id
-    , s.don_vi_goc_id    AS don_vi_goc_id
-    , s.don_vi_lket_id   AS don_vi_lket_id
-FROM dvi_link_active h
-LEFT JOIN dvi_link_sat s
-       ON s.auth_to_chuc_dvi_link_hashkey = h.auth_to_chuc_dvi_link_hashkey
+      i.business_key        AS id   
+    , g.business_key        AS don_vi_goc_id
+    , k.business_key        AS don_vi_lket_id
+FROM dvi_link_active l
+LEFT JOIN don_vi g ON g.auth_to_chuc_don_vi_hashkey = l.don_vi_goc_hashkey
+LEFT JOIN don_vi k ON k.auth_to_chuc_don_vi_hashkey = l.don_vi_lket_hashkey
+LEFT JOIN don_vi i ON i.auth_to_chuc_don_vi_hashkey = l.link_auth_to_chuc_dvi_link_hashkey
 </t>
   </si>
   <si>
@@ -789,16 +809,13 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -831,6 +848,12 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -885,13 +908,10 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1220,23 +1240,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="18.75">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
-      <c r="H1" s="54"/>
-      <c r="I1" s="54"/>
-      <c r="J1" s="54"/>
-      <c r="K1" s="54"/>
-      <c r="L1" s="54"/>
-      <c r="M1" s="54"/>
-      <c r="N1" s="54"/>
-      <c r="O1" s="54"/>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="53"/>
+      <c r="K1" s="53"/>
+      <c r="L1" s="53"/>
+      <c r="M1" s="53"/>
+      <c r="N1" s="53"/>
+      <c r="O1" s="53"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
@@ -1248,67 +1268,67 @@
     </row>
     <row r="2" spans="1:23" ht="18.75">
       <c r="A2" s="2"/>
-      <c r="B2" s="77" t="s">
+      <c r="B2" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="78"/>
+      <c r="C2" s="79"/>
       <c r="D2" s="3"/>
-      <c r="E2" s="77" t="s">
+      <c r="E2" s="78" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="78"/>
+      <c r="F2" s="79"/>
       <c r="G2" s="3"/>
-      <c r="H2" s="79" t="s">
+      <c r="H2" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="I2" s="80"/>
+      <c r="I2" s="81"/>
       <c r="J2" s="3"/>
-      <c r="K2" s="79" t="s">
+      <c r="K2" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="L2" s="80"/>
+      <c r="L2" s="81"/>
       <c r="M2" s="4"/>
-      <c r="N2" s="49" t="s">
+      <c r="N2" s="82" t="s">
         <v>5</v>
       </c>
-      <c r="O2" s="50"/>
-      <c r="P2" s="55"/>
-      <c r="Q2" s="56"/>
+      <c r="O2" s="83"/>
+      <c r="P2" s="54"/>
+      <c r="Q2" s="55"/>
       <c r="R2" s="4"/>
-      <c r="S2" s="55"/>
-      <c r="T2" s="56"/>
+      <c r="S2" s="54"/>
+      <c r="T2" s="55"/>
       <c r="U2" s="4"/>
-      <c r="V2" s="55"/>
-      <c r="W2" s="56"/>
+      <c r="V2" s="54"/>
+      <c r="W2" s="55"/>
     </row>
     <row r="3" spans="1:23" ht="18.75" customHeight="1">
       <c r="A3" s="2"/>
-      <c r="B3" s="57" t="s">
+      <c r="B3" s="56" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="58"/>
-      <c r="D3" s="51" t="s">
+      <c r="C3" s="57"/>
+      <c r="D3" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="63" t="s">
+      <c r="E3" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="64"/>
-      <c r="G3" s="51" t="s">
+      <c r="F3" s="65"/>
+      <c r="G3" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="69" t="s">
+      <c r="H3" s="70" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="70"/>
-      <c r="J3" s="51" t="s">
+      <c r="I3" s="71"/>
+      <c r="J3" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="73" t="s">
+      <c r="K3" s="74" t="s">
         <v>10</v>
       </c>
-      <c r="L3" s="74"/>
-      <c r="M3" s="51" t="s">
+      <c r="L3" s="75"/>
+      <c r="M3" s="62" t="s">
         <v>7</v>
       </c>
       <c r="N3" s="44"/>
@@ -1324,19 +1344,21 @@
     </row>
     <row r="4" spans="1:23" ht="18.75" customHeight="1">
       <c r="A4" s="5"/>
-      <c r="B4" s="59"/>
-      <c r="C4" s="60"/>
-      <c r="D4" s="52"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="66"/>
-      <c r="G4" s="52"/>
-      <c r="H4" s="69"/>
-      <c r="I4" s="70"/>
-      <c r="J4" s="52"/>
-      <c r="K4" s="75"/>
-      <c r="L4" s="76"/>
-      <c r="M4" s="52"/>
-      <c r="N4" s="44"/>
+      <c r="B4" s="58"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="63"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="63"/>
+      <c r="H4" s="70"/>
+      <c r="I4" s="71"/>
+      <c r="J4" s="63"/>
+      <c r="K4" s="76"/>
+      <c r="L4" s="77"/>
+      <c r="M4" s="63"/>
+      <c r="N4" s="44" t="s">
+        <v>11</v>
+      </c>
       <c r="O4" s="43"/>
       <c r="P4" s="4"/>
       <c r="Q4" s="4"/>
@@ -1349,20 +1371,20 @@
     </row>
     <row r="5" spans="1:23" ht="18.75" customHeight="1">
       <c r="A5" s="5"/>
-      <c r="B5" s="59"/>
-      <c r="C5" s="60"/>
-      <c r="D5" s="52"/>
-      <c r="E5" s="65"/>
-      <c r="F5" s="66"/>
-      <c r="G5" s="52"/>
-      <c r="H5" s="69"/>
-      <c r="I5" s="70"/>
-      <c r="J5" s="52"/>
-      <c r="K5" s="75"/>
-      <c r="L5" s="76"/>
-      <c r="M5" s="52"/>
+      <c r="B5" s="58"/>
+      <c r="C5" s="59"/>
+      <c r="D5" s="63"/>
+      <c r="E5" s="66"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="63"/>
+      <c r="H5" s="70"/>
+      <c r="I5" s="71"/>
+      <c r="J5" s="63"/>
+      <c r="K5" s="76"/>
+      <c r="L5" s="77"/>
+      <c r="M5" s="63"/>
       <c r="N5" s="44" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O5" s="43"/>
       <c r="P5" s="4"/>
@@ -1376,20 +1398,20 @@
     </row>
     <row r="6" spans="1:23" ht="18.75">
       <c r="A6" s="5"/>
-      <c r="B6" s="59"/>
-      <c r="C6" s="60"/>
-      <c r="D6" s="52"/>
-      <c r="E6" s="65"/>
-      <c r="F6" s="66"/>
-      <c r="G6" s="52"/>
-      <c r="H6" s="69"/>
-      <c r="I6" s="70"/>
-      <c r="J6" s="52"/>
-      <c r="K6" s="75"/>
-      <c r="L6" s="76"/>
-      <c r="M6" s="52"/>
+      <c r="B6" s="58"/>
+      <c r="C6" s="59"/>
+      <c r="D6" s="63"/>
+      <c r="E6" s="66"/>
+      <c r="F6" s="67"/>
+      <c r="G6" s="63"/>
+      <c r="H6" s="70"/>
+      <c r="I6" s="71"/>
+      <c r="J6" s="63"/>
+      <c r="K6" s="76"/>
+      <c r="L6" s="77"/>
+      <c r="M6" s="63"/>
       <c r="N6" s="44" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O6" s="43"/>
       <c r="P6" s="4"/>
@@ -1403,19 +1425,19 @@
     </row>
     <row r="7" spans="1:23" ht="18.75">
       <c r="A7" s="5"/>
-      <c r="B7" s="59"/>
-      <c r="C7" s="60"/>
-      <c r="D7" s="52"/>
-      <c r="E7" s="65"/>
-      <c r="F7" s="66"/>
-      <c r="G7" s="52"/>
-      <c r="H7" s="69"/>
-      <c r="I7" s="70"/>
-      <c r="J7" s="52"/>
-      <c r="K7" s="75"/>
-      <c r="L7" s="76"/>
-      <c r="M7" s="52"/>
-      <c r="N7" s="46"/>
+      <c r="B7" s="58"/>
+      <c r="C7" s="59"/>
+      <c r="D7" s="63"/>
+      <c r="E7" s="66"/>
+      <c r="F7" s="67"/>
+      <c r="G7" s="63"/>
+      <c r="H7" s="70"/>
+      <c r="I7" s="71"/>
+      <c r="J7" s="63"/>
+      <c r="K7" s="76"/>
+      <c r="L7" s="77"/>
+      <c r="M7" s="63"/>
+      <c r="N7" s="44"/>
       <c r="O7" s="46"/>
       <c r="P7" s="4"/>
       <c r="Q7" s="6"/>
@@ -1428,18 +1450,18 @@
     </row>
     <row r="8" spans="1:23" ht="18.75">
       <c r="A8" s="5"/>
-      <c r="B8" s="61"/>
-      <c r="C8" s="62"/>
-      <c r="D8" s="52"/>
-      <c r="E8" s="67"/>
-      <c r="F8" s="68"/>
-      <c r="G8" s="52"/>
-      <c r="H8" s="71"/>
-      <c r="I8" s="72"/>
-      <c r="J8" s="52"/>
-      <c r="K8" s="75"/>
-      <c r="L8" s="76"/>
-      <c r="M8" s="52"/>
+      <c r="B8" s="60"/>
+      <c r="C8" s="61"/>
+      <c r="D8" s="63"/>
+      <c r="E8" s="68"/>
+      <c r="F8" s="69"/>
+      <c r="G8" s="63"/>
+      <c r="H8" s="72"/>
+      <c r="I8" s="73"/>
+      <c r="J8" s="63"/>
+      <c r="K8" s="76"/>
+      <c r="L8" s="77"/>
+      <c r="M8" s="63"/>
       <c r="N8" s="46"/>
       <c r="O8" s="46"/>
       <c r="P8" s="7"/>
@@ -1554,7 +1576,7 @@
     <row r="13" spans="1:23" ht="18.75">
       <c r="A13" s="3"/>
       <c r="B13" s="12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
@@ -1562,13 +1584,13 @@
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
@@ -1588,17 +1610,17 @@
       <c r="A14" s="3"/>
       <c r="B14" s="14"/>
       <c r="C14" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
       <c r="H14" s="16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I14" s="17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J14" s="17"/>
       <c r="K14" s="3"/>
@@ -1619,7 +1641,7 @@
       <c r="A15" s="3"/>
       <c r="B15" s="19"/>
       <c r="C15" s="15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -1646,7 +1668,7 @@
       <c r="A16" s="3"/>
       <c r="B16" s="22"/>
       <c r="C16" s="15" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -1673,7 +1695,7 @@
       <c r="A17" s="3"/>
       <c r="B17" s="25"/>
       <c r="C17" s="15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
@@ -1700,7 +1722,7 @@
       <c r="A18" s="3"/>
       <c r="B18" s="26"/>
       <c r="C18" s="15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
@@ -2011,6 +2033,10 @@
     <row r="40"/>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="M3:M8"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="S2:T2"/>
     <mergeCell ref="V2:W2"/>
     <mergeCell ref="B3:C8"/>
     <mergeCell ref="D3:D8"/>
@@ -2024,10 +2050,6 @@
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="K2:L2"/>
     <mergeCell ref="N2:O2"/>
-    <mergeCell ref="M3:M8"/>
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="S2:T2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -2047,39 +2069,39 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="28" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B1" s="29" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C1" s="29" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D1" s="29" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
         <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D2" s="30"/>
     </row>
     <row r="3" spans="1:4" ht="409.6">
       <c r="A3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B3" t="s">
         <v>10</v>
       </c>
       <c r="D3" s="31" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -2106,31 +2128,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="40.5" customHeight="1">
-      <c r="A1" s="81" t="s">
-        <v>32</v>
-      </c>
-      <c r="B1" s="82"/>
-      <c r="C1" s="82"/>
-      <c r="D1" s="82"/>
-      <c r="E1" s="82"/>
-      <c r="F1" s="82"/>
+      <c r="A1" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
     </row>
     <row r="2" spans="1:6" ht="18.75">
       <c r="A2" s="32" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B2" s="32" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C2" s="32"/>
       <c r="D2" s="32" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E2" s="32" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F2" s="32" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="32.25" customHeight="1">
@@ -2150,30 +2172,30 @@
       <c r="F4" s="39"/>
     </row>
     <row r="5" spans="1:6" ht="18.75">
-      <c r="A5" s="82" t="s">
-        <v>38</v>
-      </c>
-      <c r="B5" s="82"/>
-      <c r="C5" s="82"/>
-      <c r="D5" s="82"/>
-      <c r="E5" s="83"/>
+      <c r="A5" s="50" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" s="50"/>
+      <c r="C5" s="50"/>
+      <c r="D5" s="50"/>
+      <c r="E5" s="51"/>
       <c r="F5" s="40"/>
     </row>
     <row r="6" spans="1:6" ht="18.75">
       <c r="A6" s="32" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B6" s="32" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D6" s="32" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E6" s="38" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F6" s="41"/>
     </row>
@@ -2182,16 +2204,16 @@
         <v>10</v>
       </c>
       <c r="B7" s="36" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C7" s="36" t="s">
+        <v>46</v>
+      </c>
+      <c r="D7" s="37" t="s">
+        <v>47</v>
+      </c>
+      <c r="E7" s="36" t="s">
         <v>45</v>
-      </c>
-      <c r="D7" s="37" t="s">
-        <v>46</v>
-      </c>
-      <c r="E7" s="36" t="s">
-        <v>44</v>
       </c>
       <c r="F7" s="42"/>
     </row>
@@ -2200,16 +2222,16 @@
         <v>10</v>
       </c>
       <c r="B8" s="36" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" s="36" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="C8" s="36" t="s">
-        <v>45</v>
-      </c>
-      <c r="D8" s="37" t="s">
-        <v>46</v>
-      </c>
       <c r="E8" s="36" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F8" s="42"/>
     </row>
@@ -2218,16 +2240,16 @@
         <v>10</v>
       </c>
       <c r="B9" s="36" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C9" s="36" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D9" s="37" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E9" s="36" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F9" s="42"/>
     </row>
